--- a/spec_crews/datadog_monitoring.xlsx
+++ b/spec_crews/datadog_monitoring.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jck/WORK/DEV/meta_ai_generator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jck/WORK/DEV/meta_ai_generator/spec_crews/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0EBCB7-6E7C-D74E-AE76-8802F726DF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DCFE38C-693B-D347-9460-7E960591A525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
   <si>
     <t>task_name</t>
   </si>
@@ -265,6 +265,10 @@
   </si>
   <si>
     <t>{output_path}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SendOutLookMail</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -926,7 +930,9 @@
       <c r="I5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="11"/>
+      <c r="J5" s="11" t="s">
+        <v>42</v>
+      </c>
       <c r="K5" s="11"/>
     </row>
   </sheetData>

--- a/spec_crews/datadog_monitoring.xlsx
+++ b/spec_crews/datadog_monitoring.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jck/WORK/DEV/meta_ai_generator/spec_crews/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jochungi/WORK/DEV/meta_ai_generator/spec_crews/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DCFE38C-693B-D347-9460-7E960591A525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA1544D-3124-D04F-87CA-3A70C8661D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
+    <workbookView xWindow="-560" yWindow="-19220" windowWidth="35760" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
   <sheets>
     <sheet name="spec" sheetId="3" r:id="rId1"/>
+    <sheet name="spec (2)" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -74,6 +75,42 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>jck</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{D2A8C473-E353-A543-8C64-EE166D8DAA4E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Malgun Gothic"/>
+            <family val="2"/>
+            <charset val="129"/>
+          </rPr>
+          <t>jck:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Malgun Gothic"/>
+            <family val="2"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
   <connection id="1" xr16:uid="{FDA50F79-D1D7-184E-8BF0-4FCB108457F5}" keepAlive="1" name="쿼리 - spec" description="통합 문서의 'spec' 쿼리에 대한 연결입니다." type="5" refreshedVersion="0" background="1">
@@ -83,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="46">
   <si>
     <t>task_name</t>
   </si>
@@ -271,12 +308,27 @@
     <t>SendOutLookMail</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>생성된 로그 분석 보고서를 Microsoft Outlook (또는 Google Gmail)을 통해 {recipient_email}로 전송합니다.
+    - 제목 : 애플리케이션 로그 모니터링 보고서 ({time_range})
+    - 전체 마크다운 보고서를 이메일 본문에 포함합니다(가능한 경우 HTML로 서식 지정). 
+    - 이메일이 성공적으로 전송되었는지 확인하고 전달을 확정합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그 모니터링 보고서가 포함된 이메일이 메일 서버를 통해 {recipient_email}로 성공적으로 전송되었다는 확인(Confirmation) 메시지입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모니터링 보고서의 제목, 세부정보를   메일 서버를 통해서 전송합니다.  이때 SendOutLookMail 툴에 제목, 내용, 수신자{recipient_email} 정보를 전달해야 합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -320,6 +372,14 @@
       <name val="Malgun Gothic"/>
       <family val="2"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -380,7 +440,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -424,6 +484,12 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -770,6 +836,185 @@
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="87.42578125" customWidth="1"/>
+    <col min="4" max="4" width="31.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" customWidth="1"/>
+    <col min="8" max="8" width="29.85546875" customWidth="1"/>
+    <col min="9" max="9" width="38.28515625" customWidth="1"/>
+    <col min="10" max="11" width="19.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="199" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="4"/>
+    </row>
+    <row r="3" spans="1:11" ht="164" customHeight="1">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+    </row>
+    <row r="4" spans="1:11" ht="203" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+    </row>
+    <row r="5" spans="1:11" ht="139" customHeight="1">
+      <c r="A5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" s="11"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF6A7D12-BC84-774D-A2E8-5CEC95BC3F0C}">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="21.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="74.28515625" customWidth="1"/>
     <col min="4" max="4" width="31.5703125" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" customWidth="1"/>
